--- a/AAII_Financials/Quarterly/SYF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SYF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="92">
   <si>
     <t>SYF</t>
   </si>
@@ -656,286 +656,292 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="19" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2517000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2363000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2351000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2677000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2501000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2227000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2240000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2217000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2021000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2914000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1855000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1987000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1911000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1909000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4708000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4342000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4074000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4022000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4053000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3898000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3578000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3742000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3993000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3837000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3830000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4407000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4585000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4981000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4738000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4786000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4876000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4694000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>4174000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>4244000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>4291000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>4233000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>3970000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>3913000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>3947000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>3796000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1056,53 +1062,56 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2517000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2363000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2351000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2677000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2501000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2227000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2240000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2217000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2021000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2914000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1855000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1987000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1911000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1909000</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1178,8 +1187,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1222,8 +1234,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1344,8 +1357,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1466,52 +1482,55 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>78000</v>
+      </c>
+      <c r="E14" s="3">
         <v>88000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>189000</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H14" s="3">
+        <v>34000</v>
+      </c>
+      <c r="I14" s="3">
         <v>41000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>192000</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="3">
         <v>331000</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1588,130 +1607,136 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>42500</v>
+      </c>
+      <c r="E15" s="3">
         <v>143000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>139000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>128000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>122000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>125000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>120000</v>
-      </c>
-      <c r="J15" s="3">
-        <v>121000</v>
       </c>
       <c r="K15" s="3">
         <v>121000</v>
       </c>
       <c r="L15" s="3">
+        <v>121000</v>
+      </c>
+      <c r="M15" s="3">
         <v>119000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>118000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>116000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>113000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>111000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-87000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-90000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-92000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-93000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-94000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-80000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-83000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-82000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-80000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-83000</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>-82000</v>
       </c>
       <c r="AB15" s="3">
         <v>-82000</v>
       </c>
       <c r="AC15" s="3">
-        <v>-78000</v>
+        <v>-82000</v>
       </c>
       <c r="AD15" s="3">
         <v>-78000</v>
       </c>
       <c r="AE15" s="3">
+        <v>-78000</v>
+      </c>
+      <c r="AF15" s="3">
         <v>-75000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-70000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-64000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-63000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>-29000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>-56000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>-50000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>-53000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>-48000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>-45000</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>-43000</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>-44000</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1751,252 +1776,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1253000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1228000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1210000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1248000</v>
       </c>
-      <c r="G17" s="3">
-        <v>1245000</v>
-      </c>
       <c r="H17" s="3">
+        <v>1211000</v>
+      </c>
+      <c r="I17" s="3">
         <v>1202000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1075000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1189000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1177000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1206000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>985000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1154000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1169000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1119000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1803000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1343000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>996000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>754000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>784000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>265000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>72000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>637000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1484000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1399000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1632000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1376000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1660000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1611000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1781000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1419000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1995000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1939000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1717000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1764000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1729000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1667000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1659000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1632000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1395000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>1301000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1264000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1135000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1141000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1429000</v>
       </c>
-      <c r="G18" s="3">
-        <v>1256000</v>
-      </c>
       <c r="H18" s="3">
+        <v>1290000</v>
+      </c>
+      <c r="I18" s="3">
         <v>1025000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1165000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1028000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>844000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1708000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>870000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>833000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>742000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>790000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2905000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2999000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3078000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3268000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3269000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3633000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3506000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3105000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2509000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2438000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2198000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3031000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2925000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3370000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2957000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3367000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2881000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2755000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2457000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>2480000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>2562000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>2566000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>2311000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>2281000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>2552000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>2495000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2039,8 +2071,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2083,208 +2116,214 @@
       <c r="P20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3">
         <v>-2164000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2077000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2012000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2035000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2222000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2133000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1865000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1790000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1565000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2026000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2139000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2649000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-2004000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1995000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-1828000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1905000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-1869000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-1862000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-1565000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-1633000</v>
-      </c>
-      <c r="AK20" s="3">
-        <v>-1687000</v>
       </c>
       <c r="AL20" s="3">
         <v>-1687000</v>
       </c>
       <c r="AM20" s="3">
+        <v>-1687000</v>
+      </c>
+      <c r="AN20" s="3">
         <v>-1523000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-1499000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-1644000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-1532000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1306500</v>
+      </c>
+      <c r="E21" s="3">
         <v>1278000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1280000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1557000</v>
       </c>
-      <c r="G21" s="3">
-        <v>1378000</v>
-      </c>
       <c r="H21" s="3">
+        <v>1412000</v>
+      </c>
+      <c r="I21" s="3">
         <v>1150000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1285000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1149000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>965000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1827000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>988000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>949000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>855000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>901000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>842000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1027000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1172000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1340000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1152000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1593000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1738000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1410000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1037000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>509000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>156000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>478000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1015000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1469000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1221000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1549000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1092000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>971000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>965000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>918000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>942000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>948000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>847000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>841000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>963000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>1019000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2327,8 +2366,8 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2405,252 +2444,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1186000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1047000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>952000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1429000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1256000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>984000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>973000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1028000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>844000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1708000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>539000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>833000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>742000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>790000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>741000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>922000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1066000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1233000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1047000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1500000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1641000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1315000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>944000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>412000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>59000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>382000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>921000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1375000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1129000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1462000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1012000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>893000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>892000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>847000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>875000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>879000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>788000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>782000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>908000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>963000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>301000</v>
+      </c>
+      <c r="E24" s="3">
         <v>242000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>201000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>352000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>289000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>227000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>199000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>239000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>201000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>415000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>99000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>205000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>173000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>189000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>164000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>219000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>262000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>301000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>234000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>359000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>399000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>290000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>206000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>99000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>11000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>96000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>190000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>319000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>276000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>355000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>229000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>222000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>196000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>207000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>330000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>324000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>292000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>283000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>332000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>359000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2771,252 +2819,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>885000</v>
+      </c>
+      <c r="E26" s="3">
         <v>805000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>751000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1077000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>967000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>757000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>774000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>789000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>643000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1293000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>440000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>628000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>569000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>601000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>577000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>703000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>804000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>932000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>813000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1141000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1242000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1025000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>738000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>313000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>48000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>286000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>731000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1056000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>853000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1107000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>783000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>671000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>696000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>640000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>545000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>555000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>496000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>499000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>576000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>604000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>864000</v>
+      </c>
+      <c r="E27" s="3">
         <v>784000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>730000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1057000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>946000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>736000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>753000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>768000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>624000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1282000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>429000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>618000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>559000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>590000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>567000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>692000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>793000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>922000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>803000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1130000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1232000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1014000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>728000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>303000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>37000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>275000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>731000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1056000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>853000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1107000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>783000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>671000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>696000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>640000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>545000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>555000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>496000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>499000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>576000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>604000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3137,8 +3194,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3223,8 +3283,8 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>5</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>5</v>
@@ -3241,12 +3301,12 @@
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-160000</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3259,8 +3319,11 @@
       <c r="AP29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3381,8 +3444,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3503,8 +3569,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3547,208 +3616,214 @@
       <c r="P32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3">
         <v>2164000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2077000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2012000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2035000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2222000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2133000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1865000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1790000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1565000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2026000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2139000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2649000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>2004000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1995000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>1828000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1905000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>1869000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>1862000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>1565000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>1633000</v>
-      </c>
-      <c r="AK32" s="3">
-        <v>1687000</v>
       </c>
       <c r="AL32" s="3">
         <v>1687000</v>
       </c>
       <c r="AM32" s="3">
+        <v>1687000</v>
+      </c>
+      <c r="AN32" s="3">
         <v>1523000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>1499000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>1644000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>1532000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>885000</v>
+      </c>
+      <c r="E33" s="3">
         <v>805000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>751000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1077000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>967000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>757000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>774000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>789000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>643000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1293000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>440000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>628000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>569000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>601000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>567000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>692000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>793000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>922000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>803000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1130000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1232000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1014000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>728000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>303000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>37000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>275000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>731000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1056000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>853000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1107000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>783000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>671000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>696000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>640000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>385000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>555000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>496000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>499000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>576000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>604000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3869,257 +3944,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>885000</v>
+      </c>
+      <c r="E35" s="3">
         <v>805000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>751000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1077000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>967000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>757000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>774000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>789000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>643000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1293000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>440000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>628000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>569000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>601000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>567000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>692000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>793000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>922000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>803000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1130000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1232000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1014000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>728000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>303000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>37000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>275000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>731000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1056000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>853000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1107000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>783000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>671000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>696000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>640000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>385000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>555000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>496000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>499000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>576000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>604000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4162,8 +4246,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4206,130 +4291,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16193000</v>
+      </c>
+      <c r="E41" s="3">
         <v>20559000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>14973000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>16245000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>19457000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>21629000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>14711000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>17934000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>18632000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>20021000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>14259000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>15643000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>12706000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>15303000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>10294000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>11962000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>10682000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>10541000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8337000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>9806000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>11117000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>16620000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>11524000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>13552000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>16344000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>13704000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>12147000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>11461000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>11755000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>12963000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>9396000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>12068000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>15675000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>13044000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>11602000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>13915000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>12020000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>11392000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>9321000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>13588000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4450,8 +4539,11 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4494,8 +4586,8 @@
       <c r="P43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -4572,8 +4664,11 @@
       <c r="AP43" s="3">
         <v>0</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4616,8 +4711,8 @@
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4694,8 +4789,11 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4726,20 +4824,20 @@
       <c r="L45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N45" s="3">
         <v>256000</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
+      <c r="Q45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R45" s="3">
         <v>0</v>
@@ -4816,53 +4914,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>17240000</v>
+      </c>
+      <c r="E46" s="3">
         <v>20603000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>15017000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>16479000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>20370000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>22682000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>14755000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>17981000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>18680000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>20071000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>14565000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>15800000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>12855000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>15920000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4938,53 +5039,56 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>5558000</v>
+      </c>
+      <c r="E47" s="3">
         <v>3710000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>4516000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3863000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3266000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2856000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>4023000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1160000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1454000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2419000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3624000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1721000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3459000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3370000</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
         <v>0</v>
       </c>
@@ -5060,13 +5164,16 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>5</v>
+      <c r="D48" s="3">
+        <v>117000</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>5</v>
@@ -5104,8 +5211,8 @@
       <c r="P48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
+      <c r="Q48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R48" s="3">
         <v>0</v>
@@ -5182,130 +5289,136 @@
       <c r="AP48" s="3">
         <v>0</v>
       </c>
+      <c r="AQ48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2615000</v>
+      </c>
+      <c r="E49" s="3">
         <v>2586000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2618000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2183000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2136000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2121000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2128000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2039000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2050000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1873000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1833000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2274000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2331000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2402000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2392000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2138000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2223000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2254000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2273000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2195000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2203000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2273000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2203000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2169000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2244000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2286000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2343000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2255000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2293000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2335000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2161000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2129000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1887000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1771000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1740000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1763000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>1778000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>1818000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>1661000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>1682000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5426,8 +5539,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5548,61 +5664,64 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2453000</v>
+      </c>
+      <c r="E52" s="3">
         <v>4945000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1500000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4654000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5521000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5587000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2475000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6885000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7003000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5982000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2845000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5447000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5055000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4549000</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T52" s="3">
-        <v>0</v>
+      <c r="T52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U52" s="3">
         <v>0</v>
@@ -5670,8 +5789,11 @@
       <c r="AP52" s="3">
         <v>0</v>
       </c>
+      <c r="AQ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5792,130 +5914,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>121930000</v>
+      </c>
+      <c r="E54" s="3">
         <v>121501000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>119095000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>116984000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>120505000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>122026000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>119463000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>119229000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>120489000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>121173000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>117479000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>112939000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>108697000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>107853000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>104564000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>100766000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>95200000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>95267000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>95748000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>91937000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>92017000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>95854000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>95948000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>95658000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>96544000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>98038000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>104826000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>105943000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>106388000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>105384000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>106792000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>104545000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>99122000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>95559000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>95808000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>92548000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>91140000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>89050000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>90207000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>87159000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5958,8 +6086,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6002,53 +6131,54 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>82806000</v>
+      </c>
+      <c r="E57" s="3">
         <v>82894000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>81144000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>79886000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>82262000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>83435000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>82062000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>82284000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>83100000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>83554000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>81153000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>78066000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>75765000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>74425000</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
@@ -6124,23 +6254,26 @@
       <c r="AP57" s="3">
         <v>0</v>
       </c>
+      <c r="AQ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>4350000</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>2250000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2650000</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
         <v>0</v>
       </c>
@@ -6246,8 +6379,11 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -6278,143 +6414,146 @@
       <c r="L59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N59" s="3">
         <v>107000</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R59" s="3">
         <v>5765000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5029000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4941000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4914000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5316000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4888000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4522000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4494000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4690000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4295000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4428000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4205000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4718000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4488000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4765000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4724000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4099000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4491000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3932000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3618000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>4287000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>3793000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>3214000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>2888000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>3809000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>3196000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>91251000</v>
+      </c>
+      <c r="E60" s="3">
         <v>86896000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>86925000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>86338000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>85844000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>86736000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>85456000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>85717000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>89312000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>87954000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>85516000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>82041000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>81086000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>79726000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6490,142 +6629,148 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>12082000</v>
+      </c>
+      <c r="E61" s="3">
         <v>16428000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>12932000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>11781000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>16009000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>17009000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>15462000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>15632000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>15637000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>16133000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>15982000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>15231000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>14231000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>14934000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>14191000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>14321000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>12157000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>13360000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>14507000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>12760000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>13457000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>15160000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>15775000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>15771000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>16069000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>17248000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>19866000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>20363000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>21244000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>21891000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>23996000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>23741000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>21721000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>21015000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>20799000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>19899000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>20709000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>20194000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>20147000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>20167000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E62" s="3">
+      <c r="E62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F62" s="3">
         <v>507000</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G62" s="3" t="s">
         <v>5</v>
       </c>
@@ -6641,15 +6786,15 @@
       <c r="K62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M62" s="3">
         <v>4000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7000</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>5</v>
       </c>
@@ -6665,8 +6810,8 @@
       <c r="S62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T62" s="3">
-        <v>0</v>
+      <c r="T62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U62" s="3">
         <v>0</v>
@@ -6734,8 +6879,11 @@
       <c r="AP62" s="3">
         <v>0</v>
       </c>
+      <c r="AQ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6856,8 +7004,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6978,8 +7129,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7100,130 +7254,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>105033000</v>
+      </c>
+      <c r="E66" s="3">
         <v>105024000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>102329000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>99919000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>103553000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>105445000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>102883000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>103249000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>104949000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>105891000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>103576000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>99172000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>95317000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>94660000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>91691000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>87754000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>81807000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>81849000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>82093000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>78001000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>77820000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>82415000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>83247000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>83559000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>84645000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>86068000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>89738000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>90823000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>91654000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>90675000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>92114000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>90549000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>84664000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>81203000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>81574000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>78146000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>76808000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>74687000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>76011000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>73178000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7266,8 +7426,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7388,8 +7549,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7510,13 +7674,16 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>1222000</v>
+        <v>1716000</v>
       </c>
       <c r="E70" s="3">
         <v>1222000</v>
@@ -7543,7 +7710,7 @@
         <v>1222000</v>
       </c>
       <c r="M70" s="3">
-        <v>734000</v>
+        <v>1222000</v>
       </c>
       <c r="N70" s="3">
         <v>734000</v>
@@ -7594,7 +7761,7 @@
         <v>734000</v>
       </c>
       <c r="AD70" s="3">
-        <v>0</v>
+        <v>734000</v>
       </c>
       <c r="AE70" s="3">
         <v>0</v>
@@ -7632,8 +7799,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7754,130 +7924,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>25968000</v>
+      </c>
+      <c r="E72" s="3">
         <v>25210000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>24598000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>23978000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>23036000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>22209000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>21635000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>20975000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>20310000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>19790000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>18662000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>18338000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>17828000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>17369000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>16716000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>16252000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>15679000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>15003000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>14245000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>13562000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>12560000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>11470000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>10621000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>10024000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>9852000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>9960000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>12117000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>11533000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>10627000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9939000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>8986000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>8355000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>7906000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>7334000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>6809000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>6543000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>6109000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>5724000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>5330000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>4861000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7998,8 +8174,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8120,8 +8299,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8242,130 +8424,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>15181000</v>
+      </c>
+      <c r="E76" s="3">
         <v>15255000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>15544000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>15843000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>15730000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>15359000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>15358000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>14758000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14318000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14060000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13169000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13033000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>12646000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>12459000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12139000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>12278000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>12659000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>12684000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>12921000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>13202000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>13463000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>12705000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>11967000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>11365000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>11165000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>11236000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>14354000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>15120000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>14734000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>14709000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>14678000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>13996000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>14458000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>14356000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>14234000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>14402000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>14332000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>14363000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>14196000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>13981000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8486,257 +8674,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>885000</v>
+      </c>
+      <c r="E81" s="3">
         <v>805000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>751000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1077000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>967000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>757000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>774000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>789000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>643000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1293000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>440000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>628000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>569000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>601000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>567000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>692000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>793000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>922000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>803000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1130000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1232000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1014000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>728000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>303000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>37000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>275000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>731000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1056000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>853000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1107000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>783000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>671000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>696000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>640000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>385000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>555000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>496000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>499000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>576000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>604000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8779,130 +8976,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>39000</v>
+        <v>-46000</v>
       </c>
       <c r="E83" s="3">
         <v>39000</v>
       </c>
       <c r="F83" s="3">
+        <v>39000</v>
+      </c>
+      <c r="G83" s="3">
         <v>38000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>41000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>39000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>40000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>42000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>41000</v>
       </c>
       <c r="L83" s="3">
         <v>41000</v>
       </c>
       <c r="M83" s="3">
+        <v>41000</v>
+      </c>
+      <c r="N83" s="3">
         <v>101000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>15000</v>
-      </c>
-      <c r="O83" s="3">
-        <v>14000</v>
       </c>
       <c r="P83" s="3">
         <v>14000</v>
       </c>
       <c r="Q83" s="3">
+        <v>14000</v>
+      </c>
+      <c r="R83" s="3">
         <v>101000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>105000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>106000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>107000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>105000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>93000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>97000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>95000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>93000</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>97000</v>
       </c>
       <c r="AA83" s="3">
         <v>97000</v>
       </c>
       <c r="AB83" s="3">
+        <v>97000</v>
+      </c>
+      <c r="AC83" s="3">
         <v>96000</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>94000</v>
       </c>
       <c r="AD83" s="3">
         <v>94000</v>
       </c>
       <c r="AE83" s="3">
+        <v>94000</v>
+      </c>
+      <c r="AF83" s="3">
         <v>92000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>87000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>80000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>78000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>73000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>71000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>67000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>69000</v>
-      </c>
-      <c r="AM83" s="3">
-        <v>59000</v>
       </c>
       <c r="AN83" s="3">
         <v>59000</v>
       </c>
       <c r="AO83" s="3">
+        <v>59000</v>
+      </c>
+      <c r="AP83" s="3">
         <v>55000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>56000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9023,8 +9224,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9145,8 +9349,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9267,8 +9474,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9389,8 +9599,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9511,130 +9724,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2420000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2183000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2454000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2637000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2560000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2200000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2353000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2763000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2484000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2248000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2317000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2482000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1908000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1886000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1847000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1634000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1817000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1396000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2004000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1815000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1441000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1839000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2086000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1483000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2381000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1537000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2336000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2399000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1966000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>2289000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2576000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>2685000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>2166000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1915000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>2470000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>2928000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1768000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1750000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>2036000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>1815000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9677,8 +9896,9 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9721,8 +9941,8 @@
       <c r="P91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -9799,8 +10019,11 @@
       <c r="AP91" s="3">
         <v>0</v>
       </c>
+      <c r="AQ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9921,8 +10144,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10043,130 +10269,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5187000</v>
+      </c>
+      <c r="E94" s="3">
         <v>1524000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4642000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1574000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2241000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>3603000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4963000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2231000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2507000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>798000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-7169000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2568000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5189000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>692000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-6858000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4142000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1052000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>1818000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-5764000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1834000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1853000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>4637000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3259000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3171000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>2045000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>3887000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>681000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1570000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-3182000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>3810000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-6285000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-10477000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-3029000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>755000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-7162000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1808000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-1860000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>1420000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-8169000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-3916000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10209,70 +10441,71 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>100000</v>
+      </c>
+      <c r="E96" s="3">
         <v>104000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>106000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>110000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>114000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>97000</v>
       </c>
       <c r="I96" s="3">
         <v>97000</v>
       </c>
       <c r="J96" s="3">
+        <v>97000</v>
+      </c>
+      <c r="K96" s="3">
         <v>99000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>100000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>102000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>103000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>104000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>99000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>100000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-103000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-109000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-108000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-114000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-120000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-124000</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-128000</v>
       </c>
       <c r="X96" s="3">
         <v>-128000</v>
@@ -10281,58 +10514,61 @@
         <v>-128000</v>
       </c>
       <c r="Z96" s="3">
+        <v>-128000</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-129000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-128000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-135000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-141000</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-145000</v>
       </c>
       <c r="AE96" s="3">
         <v>-145000</v>
       </c>
       <c r="AF96" s="3">
+        <v>-145000</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-150000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-151000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-156000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-113000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-114000</v>
-      </c>
-      <c r="AK96" s="3">
-        <v>-118000</v>
       </c>
       <c r="AL96" s="3">
         <v>-118000</v>
       </c>
       <c r="AM96" s="3">
-        <v>-105000</v>
+        <v>-118000</v>
       </c>
       <c r="AN96" s="3">
         <v>-105000</v>
       </c>
       <c r="AO96" s="3">
+        <v>-105000</v>
+      </c>
+      <c r="AP96" s="3">
         <v>-107000</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10453,8 +10689,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10575,8 +10814,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10697,130 +10939,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-596000</v>
+      </c>
+      <c r="E100" s="3">
         <v>1879000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>918000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4955000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2817000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2119000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-617000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1231000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1367000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2604000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3473000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>3031000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>216000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2912000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2380000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>4779000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-899000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-976000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2546000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1623000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-5148000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-979000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-848000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1100000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1796000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-4287000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2091000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1253000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>68000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-3182000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1814000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>4173000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>2579000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-313000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>2380000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>281000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>1284000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-829000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>1866000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>3902000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10863,8 +11111,8 @@
       <c r="P101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10941,126 +11189,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3363000</v>
+      </c>
+      <c r="E102" s="3">
         <v>5586000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1270000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3892000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2498000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>7922000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3227000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-699000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1390000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>5650000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1379000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2945000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3065000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>5490000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2631000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2271000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-134000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2238000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1214000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1642000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-5560000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>5497000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2021000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-2788000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>2630000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1137000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>926000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-424000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1148000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>2917000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1895000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-3619000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1716000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>2357000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-2313000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>1375000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>1148000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>2071000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-4267000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>1801000</v>
       </c>
     </row>
